--- a/Hero_Hub_UI_Testing/src/test/resources/TestData/OrangeHrmTestData.xlsx
+++ b/Hero_Hub_UI_Testing/src/test/resources/TestData/OrangeHrmTestData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Username</t>
   </si>
@@ -27,6 +27,24 @@
   </si>
   <si>
     <t>admin123</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>admin1234</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>Invalid ID</t>
+  </si>
+  <si>
+    <t>Invalid Pass</t>
   </si>
 </sst>
 </file>
@@ -59,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -93,8 +111,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,27 +417,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.453125" customWidth="1"/>
     <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
